--- a/classification_report.xlsx
+++ b/classification_report.xlsx
@@ -453,17 +453,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>change_user_name</t>
+          <t>what_is_your_name</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="n">
         <v>30</v>
@@ -472,17 +472,17 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>what_is_your_name</t>
+          <t>oil_change_how</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.40625</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="E3" t="n">
         <v>30</v>
@@ -491,17 +491,17 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>user_name</t>
+          <t>change_user_name</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4042553191489361</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4935064935064935</v>
       </c>
       <c r="E4" t="n">
         <v>30</v>
@@ -514,13 +514,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.3466666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5434782608695652</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="E5" t="n">
         <v>30</v>
@@ -529,17 +529,17 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>make_call</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
@@ -548,17 +548,17 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>todo_list_update</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="E7" t="n">
         <v>30</v>
@@ -567,17 +567,17 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>where_are_you_from</t>
+          <t>shopping_list</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5277777777777778</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="E8" t="n">
         <v>30</v>
@@ -586,17 +586,17 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>todo_list</t>
+          <t>change_ai_name</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.6101694915254238</v>
       </c>
       <c r="E9" t="n">
         <v>30</v>
@@ -605,17 +605,17 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>distance</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.75</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.6274509803921569</v>
       </c>
       <c r="E10" t="n">
         <v>30</v>
@@ -624,17 +624,17 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>shopping_list</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.6274509803921569</v>
       </c>
       <c r="E11" t="n">
         <v>30</v>
@@ -643,17 +643,17 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>todo_list_update</t>
+          <t>restaurant_reviews</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6382978723404256</v>
       </c>
       <c r="E12" t="n">
         <v>30</v>
@@ -662,17 +662,17 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>restaurant_reviews</t>
+          <t>travel_suggestion</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.6461538461538462</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
@@ -681,17 +681,17 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>change_ai_name</t>
+          <t>play_music</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.55</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.6530612244897959</v>
       </c>
       <c r="E14" t="n">
         <v>30</v>
@@ -700,17 +700,17 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>calendar</t>
+          <t>meal_suggestion</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.65625</v>
       </c>
       <c r="E15" t="n">
         <v>30</v>
@@ -719,17 +719,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>goodbye</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5476190476190477</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E16" t="n">
         <v>30</v>
@@ -738,17 +738,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>translate</t>
+          <t>make_call</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>0.64</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="E17" t="n">
         <v>30</v>
@@ -757,17 +757,17 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>todo_list</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6530612244897959</v>
+        <v>0.6865671641791045</v>
       </c>
       <c r="E18" t="n">
         <v>30</v>
@@ -776,17 +776,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>travel_suggestion</t>
+          <t>where_are_you_from</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.6875</v>
       </c>
       <c r="E19" t="n">
         <v>30</v>
@@ -795,17 +795,17 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>greeting</t>
+          <t>shopping_list_update</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="E20" t="n">
         <v>30</v>
@@ -814,7 +814,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>report_fraud</t>
+          <t>what_can_i_ask_you</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -833,7 +833,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>play_music</t>
+          <t>translate</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -852,17 +852,17 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>distance</t>
+          <t>oil_change_when</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="E23" t="n">
         <v>30</v>
@@ -871,17 +871,17 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>meal_suggestion</t>
+          <t>restaurant_reservation</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.711864406779661</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
@@ -890,17 +890,17 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bill_due</t>
+          <t>report_fraud</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E25" t="n">
         <v>30</v>
@@ -909,17 +909,17 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>what_can_i_ask_you</t>
+          <t>greeting</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.9</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7384615384615385</v>
+        <v>0.72</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
@@ -928,17 +928,17 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bill_balance</t>
+          <t>calendar</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7450980392156863</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E27" t="n">
         <v>30</v>
@@ -947,17 +947,17 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>restaurant_suggestion</t>
+          <t>order</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="D28" t="n">
-        <v>0.75</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E28" t="n">
         <v>30</v>
@@ -966,17 +966,17 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>account_blocked</t>
+          <t>who_do_you_work_for</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.75</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="E29" t="n">
         <v>30</v>
@@ -985,17 +985,17 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>shopping_list_update</t>
+          <t>goodbye</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="E30" t="n">
         <v>30</v>
@@ -1004,17 +1004,17 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>bill_due</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.75</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1023,17 +1023,17 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>reminder_update</t>
+          <t>current_location</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.7536231884057971</v>
       </c>
       <c r="E32" t="n">
         <v>30</v>
@@ -1042,17 +1042,17 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>ingredients_list</t>
+          <t>share_location</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.95</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.76</v>
       </c>
       <c r="E33" t="n">
         <v>30</v>
@@ -1061,17 +1061,17 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>card_declined</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7636363636363637</v>
+        <v>0.76</v>
       </c>
       <c r="E34" t="n">
         <v>30</v>
@@ -1080,17 +1080,17 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>damaged_card</t>
+          <t>restaurant_suggestion</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="E35" t="n">
         <v>30</v>
@@ -1099,17 +1099,17 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>new_card</t>
+          <t>no</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="D36" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7636363636363637</v>
       </c>
       <c r="E36" t="n">
         <v>30</v>
@@ -1118,17 +1118,17 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>who_do_you_work_for</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7719298245614035</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="E37" t="n">
         <v>30</v>
@@ -1137,17 +1137,17 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>schedule_meeting</t>
+          <t>income</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="E38" t="n">
         <v>30</v>
@@ -1156,17 +1156,17 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>replacement_card_duration</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.875</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="E39" t="n">
         <v>30</v>
@@ -1175,17 +1175,17 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>change_language</t>
+          <t>bill_balance</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="E40" t="n">
         <v>30</v>
@@ -1194,7 +1194,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>card_declined</t>
+          <t>how_busy</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1213,17 +1213,17 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>improve_credit_score</t>
+          <t>spending_history</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7843137254901961</v>
+        <v>0.7868852459016393</v>
       </c>
       <c r="E42" t="n">
         <v>30</v>
@@ -1232,17 +1232,17 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>freeze_account</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7868852459016393</v>
+        <v>0.7887323943661971</v>
       </c>
       <c r="E43" t="n">
         <v>30</v>
@@ -1251,17 +1251,17 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>who_made_you</t>
+          <t>directions</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7868852459016393</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="E44" t="n">
         <v>30</v>
@@ -1270,17 +1270,17 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>calendar_update</t>
+          <t>new_card</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.8</v>
       </c>
       <c r="E45" t="n">
         <v>30</v>
@@ -1289,17 +1289,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>spending_history</t>
+          <t>ingredients_list</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8214285714285714</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.8</v>
       </c>
       <c r="E46" t="n">
         <v>30</v>
@@ -1308,17 +1308,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>repeat</t>
+          <t>damaged_card</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.8</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7936507936507936</v>
+        <v>0.8</v>
       </c>
       <c r="E47" t="n">
         <v>30</v>
@@ -1327,17 +1327,17 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>restaurant_reservation</t>
+          <t>redeem_rewards</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.8</v>
       </c>
       <c r="C48" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7936507936507936</v>
+        <v>0.8</v>
       </c>
       <c r="E48" t="n">
         <v>30</v>
@@ -1346,17 +1346,17 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>freeze_account</t>
+          <t>w2</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8</v>
+        <v>0.8059701492537313</v>
       </c>
       <c r="E49" t="n">
         <v>30</v>
@@ -1365,17 +1365,17 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>change_volume</t>
+          <t>who_made_you</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8</v>
+        <v>0.78125</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D50" t="n">
-        <v>0.8</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="E50" t="n">
         <v>30</v>
@@ -1384,17 +1384,17 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>oil_change_how</t>
+          <t>repeat</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.78125</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="E51" t="n">
         <v>30</v>
@@ -1403,17 +1403,17 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>w2</t>
+          <t>improve_credit_score</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8059701492537313</v>
+        <v>0.8070175438596491</v>
       </c>
       <c r="E52" t="n">
         <v>30</v>
@@ -1422,7 +1422,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>payday</t>
+          <t>cook_time</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1441,7 +1441,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>travel_notification</t>
+          <t>book_flight</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1460,17 +1460,17 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>share_location</t>
+          <t>smart_home</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.75</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="E55" t="n">
         <v>30</v>
@@ -1479,17 +1479,17 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>replacement_card_duration</t>
+          <t>change_language</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.75</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D56" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="E56" t="n">
         <v>30</v>
@@ -1498,17 +1498,17 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>cook_time</t>
+          <t>rewards_balance</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.819672131147541</v>
       </c>
       <c r="E57" t="n">
         <v>30</v>
@@ -1517,17 +1517,17 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>oil_change_when</t>
+          <t>reminder_update</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D58" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="E58" t="n">
         <v>30</v>
@@ -1536,17 +1536,17 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>reminder</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="E59" t="n">
         <v>30</v>
@@ -1555,17 +1555,17 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>how_busy</t>
+          <t>food_last</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D60" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E60" t="n">
         <v>30</v>
@@ -1574,17 +1574,17 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>pay_bill</t>
+          <t>payday</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E61" t="n">
         <v>30</v>
@@ -1593,74 +1593,74 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>pto_request_status</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.842</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8</v>
+        <v>0.842</v>
       </c>
       <c r="D62" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.842</v>
       </c>
       <c r="E62" t="n">
-        <v>30</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>meeting_schedule</t>
+          <t>macro avg</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.8568324481053822</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8420000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>0.8301886792452831</v>
+        <v>0.8422531542575413</v>
       </c>
       <c r="E63" t="n">
-        <v>30</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>pin_change</t>
+          <t>weighted avg</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.8568324481053822</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.842</v>
       </c>
       <c r="D64" t="n">
-        <v>0.8301886792452831</v>
+        <v>0.8422531542575413</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>redeem_rewards</t>
+          <t>calendar_update</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="D65" t="n">
-        <v>0.8301886792452831</v>
+        <v>0.84375</v>
       </c>
       <c r="E65" t="n">
         <v>30</v>
@@ -1669,17 +1669,17 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>pto_balance</t>
+          <t>update_playlist</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8307692307692308</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="E66" t="n">
         <v>30</v>
@@ -1688,17 +1688,17 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>what_are_your_hobbies</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8524590163934426</v>
       </c>
       <c r="E67" t="n">
         <v>30</v>
@@ -1707,17 +1707,17 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>pto_request_status</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.92</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8363636363636363</v>
+        <v>0.8524590163934426</v>
       </c>
       <c r="E68" t="n">
         <v>30</v>
@@ -1726,74 +1726,74 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>weighted avg</t>
+          <t>accept_reservations</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8514869921019785</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="C69" t="n">
-        <v>0.838</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8377335484139302</v>
+        <v>0.8524590163934426</v>
       </c>
       <c r="E69" t="n">
-        <v>4500</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>macro avg</t>
+          <t>pay_bill</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8514869921019785</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="C70" t="n">
-        <v>0.838</v>
+        <v>0.9</v>
       </c>
       <c r="D70" t="n">
-        <v>0.8377335484139302</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E70" t="n">
-        <v>4500</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>travel_notification</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.838</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="C71" t="n">
-        <v>0.838</v>
+        <v>0.8</v>
       </c>
       <c r="D71" t="n">
-        <v>0.838</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E71" t="n">
-        <v>0.838</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>what_are_your_hobbies</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D72" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="E72" t="n">
         <v>30</v>
@@ -1802,17 +1802,17 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>how_old_are_you</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D73" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="E73" t="n">
         <v>30</v>
@@ -1821,17 +1821,17 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accept_reservations</t>
+          <t>next_song</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8125</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="E74" t="n">
         <v>30</v>
@@ -1840,17 +1840,17 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.84375</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D75" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="E75" t="n">
         <v>30</v>
@@ -1859,17 +1859,17 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>change_speed</t>
+          <t>thank_you</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.84375</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8450704225352113</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="E76" t="n">
         <v>30</v>
@@ -1878,17 +1878,17 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>order_status</t>
+          <t>pto_request</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.84375</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="E77" t="n">
         <v>30</v>
@@ -1897,17 +1897,17 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>update_playlist</t>
+          <t>transfer</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.84375</v>
       </c>
       <c r="C78" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D78" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="E78" t="n">
         <v>30</v>
@@ -1916,17 +1916,17 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>next_holiday</t>
+          <t>credit_score</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.875</v>
       </c>
       <c r="E79" t="n">
         <v>30</v>
@@ -1935,17 +1935,17 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>rewards_balance</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="E80" t="n">
         <v>30</v>
@@ -1954,17 +1954,17 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>smart_home</t>
+          <t>international_visa</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="E81" t="n">
         <v>30</v>
@@ -1973,17 +1973,17 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>pto_request</t>
+          <t>schedule_meeting</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D82" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="E82" t="n">
         <v>30</v>
@@ -1992,17 +1992,17 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>current_location</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D83" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="E83" t="n">
         <v>30</v>
@@ -2011,17 +2011,17 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>credit_score</t>
+          <t>confirm_reservation</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8656716417910447</v>
+        <v>0.8813559322033898</v>
       </c>
       <c r="E84" t="n">
         <v>30</v>
@@ -2030,17 +2030,17 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>expiration_date</t>
+          <t>account_blocked</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="C85" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="D85" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8813559322033898</v>
       </c>
       <c r="E85" t="n">
         <v>30</v>
@@ -2049,17 +2049,17 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>food_last</t>
+          <t>weather</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0.8679245283018868</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E86" t="n">
         <v>30</v>
@@ -2068,17 +2068,17 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>sync_device</t>
+          <t>pto_balance</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.96</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D87" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="E87" t="n">
         <v>30</v>
@@ -2087,17 +2087,17 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>directions</t>
+          <t>change_volume</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8235294117647058</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="D88" t="n">
-        <v>0.875</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E88" t="n">
         <v>30</v>
@@ -2106,17 +2106,17 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>transfer</t>
+          <t>pin_change</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.9259259259259259</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="D89" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E89" t="n">
         <v>30</v>
@@ -2125,17 +2125,17 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>find_phone</t>
+          <t>alarm</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D90" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8923076923076924</v>
       </c>
       <c r="E90" t="n">
         <v>30</v>
@@ -2144,17 +2144,17 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>thank_you</t>
+          <t>book_hotel</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D91" t="n">
-        <v>0.8852459016393442</v>
+        <v>0.8923076923076924</v>
       </c>
       <c r="E91" t="n">
         <v>30</v>
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>credit_limit</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D92" t="n">
-        <v>0.8852459016393442</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E92" t="n">
         <v>30</v>
@@ -2182,17 +2182,17 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>book_flight</t>
+          <t>schedule_maintenance</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C93" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D93" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E93" t="n">
         <v>30</v>
@@ -2201,17 +2201,17 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>confirm_reservation</t>
+          <t>ingredient_substitution</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D94" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E94" t="n">
         <v>30</v>
@@ -2220,17 +2220,17 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>definition</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D95" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E95" t="n">
         <v>30</v>
@@ -2239,17 +2239,17 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>next_song</t>
+          <t>reminder</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="C96" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D96" t="n">
-        <v>0.8923076923076924</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="E96" t="n">
         <v>30</v>
@@ -2258,17 +2258,17 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>ingredient_substitution</t>
+          <t>how_old_are_you</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.9</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="D97" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.9</v>
       </c>
       <c r="E97" t="n">
         <v>30</v>
@@ -2277,17 +2277,17 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>international_visa</t>
+          <t>meaning_of_life</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D98" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9</v>
       </c>
       <c r="E98" t="n">
         <v>30</v>
@@ -2296,17 +2296,17 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>whisper_mode</t>
+          <t>pto_used</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.9</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D99" t="n">
-        <v>0.90625</v>
+        <v>0.9</v>
       </c>
       <c r="E99" t="n">
         <v>30</v>
@@ -2315,17 +2315,17 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>cancel_reservation</t>
+          <t>expiration_date</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.9</v>
       </c>
       <c r="C100" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D100" t="n">
-        <v>0.90625</v>
+        <v>0.9</v>
       </c>
       <c r="E100" t="n">
         <v>30</v>
@@ -2334,17 +2334,17 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>pto_used</t>
+          <t>tire_pressure</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.875</v>
       </c>
       <c r="C101" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D101" t="n">
-        <v>0.90625</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="E101" t="n">
         <v>30</v>
@@ -2353,17 +2353,17 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="E102" t="n">
         <v>30</v>
@@ -2372,17 +2372,17 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>definition</t>
+          <t>spelling</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="C103" t="n">
-        <v>0.9</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9152542372881356</v>
+        <v>0.90625</v>
       </c>
       <c r="E103" t="n">
         <v>30</v>
@@ -2391,17 +2391,17 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>what_song</t>
+          <t>report_lost_card</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.9032258064516129</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9180327868852459</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="E104" t="n">
         <v>30</v>
@@ -2410,17 +2410,17 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>car_rental</t>
+          <t>sync_device</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D105" t="n">
-        <v>0.9206349206349206</v>
+        <v>0.9122807017543859</v>
       </c>
       <c r="E105" t="n">
         <v>30</v>
@@ -2429,17 +2429,17 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>alarm</t>
+          <t>gas_type</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E106" t="n">
         <v>30</v>
@@ -2448,17 +2448,17 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>apr</t>
+          <t>find_phone</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9206349206349206</v>
       </c>
       <c r="E107" t="n">
         <v>30</v>
@@ -2467,7 +2467,7 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>nutrition_info</t>
+          <t>change_speed</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2486,7 +2486,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>car_rental</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2505,7 +2505,7 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>report_lost_card</t>
+          <t>plug_type</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2524,17 +2524,17 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>travel_alert</t>
+          <t>fun_fact</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="C111" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="E111" t="n">
         <v>30</v>
@@ -2543,17 +2543,17 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>carry_on</t>
+          <t>rollover_401k</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="E112" t="n">
         <v>30</v>
@@ -2562,17 +2562,17 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>credit_limit_change</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E113" t="n">
         <v>30</v>
@@ -2600,7 +2600,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>international_fees</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2619,17 +2619,17 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>timer</t>
+          <t>next_holiday</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.90625</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C116" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E116" t="n">
         <v>30</v>
@@ -2638,7 +2638,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>uber</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2657,17 +2657,17 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>book_hotel</t>
+          <t>timer</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.90625</v>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9375</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="E118" t="n">
         <v>30</v>
@@ -2676,17 +2676,17 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>meaning_of_life</t>
+          <t>credit_limit</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>0.90625</v>
       </c>
       <c r="C119" t="n">
-        <v>0.9</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D119" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="E119" t="n">
         <v>30</v>
@@ -2695,17 +2695,17 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>plug_type</t>
+          <t>what_song</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.90625</v>
       </c>
       <c r="C120" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9491525423728814</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="E120" t="n">
         <v>30</v>
@@ -2714,17 +2714,17 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>do_you_have_pets</t>
+          <t>lost_luggage</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="C121" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9375</v>
       </c>
       <c r="E121" t="n">
         <v>30</v>
@@ -2733,17 +2733,17 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>vaccines</t>
+          <t>meeting_schedule</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.9354838709677419</v>
+        <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="E122" t="n">
         <v>30</v>
@@ -2752,17 +2752,17 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>schedule_maintenance</t>
+          <t>travel_alert</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.9354838709677419</v>
+        <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D123" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="E123" t="n">
         <v>30</v>
@@ -2771,17 +2771,17 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>international_fees</t>
+          <t>carry_on</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.9354838709677419</v>
+        <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="E124" t="n">
         <v>30</v>
@@ -2790,17 +2790,17 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>last_maintenance</t>
+          <t>order_status</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="C125" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9491525423728814</v>
       </c>
       <c r="E125" t="n">
         <v>30</v>
@@ -2809,17 +2809,17 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>order_checks</t>
+          <t>insurance_change</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D126" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9491525423728814</v>
       </c>
       <c r="E126" t="n">
         <v>30</v>
@@ -2828,17 +2828,17 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>flight_status</t>
+          <t>interest_rate</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9491525423728814</v>
       </c>
       <c r="E127" t="n">
         <v>30</v>
@@ -2847,17 +2847,17 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>rollover_401k</t>
+          <t>timezone</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="C128" t="n">
         <v>0.9333333333333333</v>
       </c>
       <c r="D128" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9491525423728814</v>
       </c>
       <c r="E128" t="n">
         <v>30</v>
@@ -2866,17 +2866,17 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>reset_settings</t>
+          <t>flight_status</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="C129" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9508196721311475</v>
       </c>
       <c r="E129" t="n">
         <v>30</v>
@@ -2885,17 +2885,17 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>interest_rate</t>
+          <t>nutrition_info</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="C130" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9508196721311475</v>
       </c>
       <c r="E130" t="n">
         <v>30</v>
@@ -2904,17 +2904,17 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>fun_fact</t>
+          <t>application_status</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="C131" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9508196721311475</v>
       </c>
       <c r="E131" t="n">
         <v>30</v>
@@ -2923,17 +2923,17 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>gas_type</t>
+          <t>apr</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="C132" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="E132" t="n">
         <v>30</v>
@@ -2942,17 +2942,17 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>application_status</t>
+          <t>order_checks</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="C133" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="E133" t="n">
         <v>30</v>
@@ -2961,17 +2961,17 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>credit_limit_change</t>
+          <t>vaccines</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="C134" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="E134" t="n">
         <v>30</v>
@@ -2980,17 +2980,17 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>taxes</t>
+          <t>last_maintenance</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D135" t="n">
-        <v>0.967741935483871</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="E135" t="n">
         <v>30</v>
@@ -2999,17 +2999,17 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>tire_change</t>
+          <t>are_you_a_bot</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.9375</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D136" t="n">
-        <v>0.967741935483871</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="E136" t="n">
         <v>30</v>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C137" t="n">
         <v>0.9666666666666667</v>
       </c>
       <c r="D137" t="n">
-        <v>0.9830508474576272</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="E137" t="n">
         <v>30</v>
@@ -3037,17 +3037,17 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>min_payment</t>
+          <t>whisper_mode</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C138" t="n">
         <v>0.9666666666666667</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9830508474576272</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="E138" t="n">
         <v>30</v>
@@ -3056,17 +3056,17 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>calories</t>
+          <t>min_payment</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C139" t="n">
         <v>0.9666666666666667</v>
       </c>
       <c r="D139" t="n">
-        <v>0.9830508474576272</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="E139" t="n">
         <v>30</v>
@@ -3075,17 +3075,17 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>are_you_a_bot</t>
+          <t>tell_joke</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="C140" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>0.9830508474576272</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="E140" t="n">
         <v>30</v>
@@ -3094,17 +3094,17 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>insurance_change</t>
+          <t>taxes</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="C141" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9830508474576272</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="E141" t="n">
         <v>30</v>
@@ -3113,7 +3113,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>spelling</t>
+          <t>reset_settings</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3132,7 +3132,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>measurement_conversion</t>
+          <t>calories</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3151,17 +3151,17 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>mpg</t>
+          <t>cancel_reservation</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.967741935483871</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="E144" t="n">
         <v>30</v>
@@ -3170,17 +3170,17 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>lost_luggage</t>
+          <t>tire_change</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.967741935483871</v>
+        <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="E145" t="n">
         <v>30</v>
@@ -3189,17 +3189,17 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>uber</t>
+          <t>measurement_conversion</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.967741935483871</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="E146" t="n">
         <v>30</v>
@@ -3208,17 +3208,17 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>tell_joke</t>
+          <t>roll_dice</t>
         </is>
       </c>
       <c r="B147" t="n">
         <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="E147" t="n">
         <v>30</v>
@@ -3227,17 +3227,17 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>routing</t>
+          <t>do_you_have_pets</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0.9836065573770492</v>
       </c>
       <c r="E148" t="n">
         <v>30</v>
@@ -3246,17 +3246,17 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>roll_dice</t>
+          <t>mpg</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0.9836065573770492</v>
       </c>
       <c r="E149" t="n">
         <v>30</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0.9836065573770492</v>
       </c>
       <c r="E150" t="n">
         <v>30</v>
@@ -3341,7 +3341,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>tire_pressure</t>
+          <t>routing</t>
         </is>
       </c>
       <c r="B154" t="n">
